--- a/Desktop/客户开发跟踪表.xlsx
+++ b/Desktop/客户开发跟踪表.xlsx
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -780,12 +780,12 @@
         <v>2</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="4" t="inlineStr"/>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13（等5天再跟）</t>
+          <t>2026-07-20（Round 3）</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
@@ -981,17 +981,17 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn InMail</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>D01S 牙科模型树脂 - 加入 FiLAMONT 产品线</t>
+          <t>D01S dental model resin — for your FiLAMONT lineup</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>一直在关注 Protomont 的成长。D01S 适合 FiLAMONT 产品线：92D硬度、免喷扫描、开放系统385-405nm。</t>
+          <t>harsh@protomont.com | Hi Harsh,一直在关注Protomont。D01S适合FiLAMONT产品线：92D硬度、直接扫描、开放系统385-405nm。</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -1003,12 +1003,12 @@
         <v>2</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="4" t="inlineStr"/>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10（发TDS软跟进）</t>
+          <t>2026-07-17（Round 3）</t>
         </is>
       </c>
       <c r="P9" s="8" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>打开2次。发 D01S TDS 做软跟进不催回复。话术：Here is the TDS for D01S. Flexural 39MPa, 92 Shore D. Works with Phrozen/Elegoo/Anycubic.</t>
+          <t>harsh@protomont.com | 打开2次。发 D01S TDS 做软跟进不催回复。话术：Here is the TDS for D01S. Flexural 39MPa, 92 Shore D. Works with Phrozen/Elegoo/Anycubic.</t>
         </is>
       </c>
     </row>
@@ -1392,6 +1392,86 @@
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>赛道不匹配。做handpiece，不消耗树脂。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Dylan Hao</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Co-founder / CEO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>JS Dental Lab (Ampower Dental Laboratories LLC)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>美国 (Hayward, CA / Bayside, NY)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DTC牙科品牌 / 数字化技工所</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Your thermoform model resin</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>认同Premium 3D技术栈 → 点出模型树脂成本矛盾 → 问他在用什么模型树脂</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>已发送</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-07-16（3天后Round 2）</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>DTC夜磨牙套品牌，深度应用3D打印。CEO Dylan Hao亲力亲为，Quora牙科KOL。已从中国进口PVS/膜片。目标：热成型模型树脂替代。邮箱：dylan@jsdentallab.com / 手机：+1 510-996-2634</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1430,6 +1510,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
@@ -1465,7 +1546,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10（发TDS软跟进）</t>
+          <t>2026-07-17（Round 3）</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1490,14 +1571,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>打开2次。发 D01S TDS 做软跟进不催回复。话术：Here is the TDS for D01S. Flexural 39MPa, 92 Shore D. Works with Phrozen/Elegoo/Anycubic.</t>
+          <t>Round 3: 发D01S完整TDS。Round 2已发核心数据(39MPa/92D/开放系统)。harsh@protomont.com</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13（等5天再跟）</t>
+          <t>2026-07-20（Round 3）</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1522,7 +1603,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>打开了2次，兴趣度高。同时联系了 Richie 和 Ronald。Follow-up 话术：just checking if D01S still on your radar. Happy to send sample to SG this week.</t>
+          <t>Round 3: 发D01S行业对比数据+案例。Round 2已发产品册链接。InMail: asked about supplier rotation, offered catalog.</t>
         </is>
       </c>
     </row>
@@ -1619,6 +1700,38 @@
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>信息太少，公司名未知。需要更多背景调查才能判断合作可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-16（3天后Round 2）</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>JS Dental Lab (Ampower Dental Laboratories LLC)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>已发送</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Round 2: 发行业数据/TDS对比，不同角度。DTC夜磨牙套品牌，已深度使用3D打印。邮箱：dylan@jsdentallab.com</t>
         </is>
       </c>
     </row>
